--- a/data/trans_dic/P17A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P17A-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,86; 23,1</t>
+          <t>14,15; 23,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,45; 26,19</t>
+          <t>15,87; 25,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,6; 28,79</t>
+          <t>18,58; 29,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 29,3</t>
+          <t>16,35; 25,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,37; 30,83</t>
+          <t>20,39; 31,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,39; 38,79</t>
+          <t>27,87; 39,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,61; 37,85</t>
+          <t>26,96; 38,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,28; 31,22</t>
+          <t>21,7; 30,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 25,43</t>
+          <t>18,33; 25,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,48; 31,01</t>
+          <t>23,55; 31,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 32,04</t>
+          <t>23,91; 31,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,88; 28,41</t>
+          <t>20,38; 26,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 22,1</t>
+          <t>14,71; 21,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,46; 25,44</t>
+          <t>17,07; 25,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 26,1</t>
+          <t>18,17; 25,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 19,96</t>
+          <t>12,48; 20,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 30,28</t>
+          <t>22,44; 30,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,91; 34,21</t>
+          <t>25,85; 34,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,32; 38,8</t>
+          <t>30,54; 39,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,98; 22,18</t>
+          <t>15,75; 21,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,06; 25,31</t>
+          <t>19,68; 25,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,88; 28,6</t>
+          <t>22,87; 28,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,39; 31,39</t>
+          <t>25,53; 31,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,78; 19,83</t>
+          <t>14,78; 19,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 21,71</t>
+          <t>12,93; 21,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,93; 32,13</t>
+          <t>22,11; 32,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 28,07</t>
+          <t>19,08; 28,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,91; 24,28</t>
+          <t>16,53; 24,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,44; 35,29</t>
+          <t>25,82; 35,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,46; 47,4</t>
+          <t>36,83; 47,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,33; 36,57</t>
+          <t>26,55; 36,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,55</t>
+          <t>18,56; 25,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,69; 27,31</t>
+          <t>20,49; 27,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,89; 38,28</t>
+          <t>30,95; 38,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,86; 30,82</t>
+          <t>24,31; 31,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,07; 23,82</t>
+          <t>18,34; 23,91</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 18,89</t>
+          <t>11,24; 18,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 23,56</t>
+          <t>15,16; 23,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 28,9</t>
+          <t>19,84; 29,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 28,19</t>
+          <t>17,91; 28,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,25; 37,17</t>
+          <t>27,61; 37,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,25; 34,81</t>
+          <t>25,34; 34,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,36; 40,31</t>
+          <t>30,29; 39,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,71; 58,91</t>
+          <t>22,82; 31,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,61; 26,86</t>
+          <t>20,69; 26,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 27,48</t>
+          <t>21,58; 27,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 33,53</t>
+          <t>26,23; 32,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,49; 49,44</t>
+          <t>21,66; 28,05</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 28,26</t>
+          <t>16,9; 28,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 31,08</t>
+          <t>18,34; 31,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 19,14</t>
+          <t>9,9; 20,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 14,2</t>
+          <t>6,55; 13,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,61; 43,82</t>
+          <t>30,03; 43,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,02; 48,5</t>
+          <t>34,92; 47,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,59; 29,61</t>
+          <t>18,25; 29,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,01</t>
+          <t>10,39; 16,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,0; 34,02</t>
+          <t>25,33; 34,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,41; 38,12</t>
+          <t>28,49; 38,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 22,96</t>
+          <t>15,79; 23,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,66</t>
+          <t>9,21; 14,27</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,99; 21,66</t>
+          <t>13,24; 22,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,33; 35,05</t>
+          <t>24,5; 35,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,34; 47,19</t>
+          <t>35,27; 47,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,29; 23,99</t>
+          <t>15,32; 23,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,61; 36,78</t>
+          <t>25,56; 36,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,83; 44,83</t>
+          <t>33,74; 45,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,82; 54,16</t>
+          <t>41,77; 53,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,01; 26,89</t>
+          <t>18,71; 26,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,56; 27,79</t>
+          <t>20,42; 27,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,26; 38,28</t>
+          <t>30,64; 38,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39,82; 48,71</t>
+          <t>40,33; 48,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,27; 24,33</t>
+          <t>18,0; 23,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,19; 27,24</t>
+          <t>20,33; 27,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,18; 29,1</t>
+          <t>21,81; 28,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,57; 26,36</t>
+          <t>19,4; 26,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,14; 26,91</t>
+          <t>19,49; 26,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,06; 37,32</t>
+          <t>30,0; 37,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,72; 35,72</t>
+          <t>28,38; 35,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,62; 30,59</t>
+          <t>23,61; 30,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,4; 31,48</t>
+          <t>28,36; 34,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,17; 31,18</t>
+          <t>26,24; 31,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,41; 31,25</t>
+          <t>26,21; 31,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,31; 27,62</t>
+          <t>22,47; 27,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,61; 27,66</t>
+          <t>24,74; 29,51</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,29; 27,23</t>
+          <t>21,07; 27,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,31; 23,27</t>
+          <t>17,25; 23,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,52; 31,86</t>
+          <t>25,71; 32,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 21,63</t>
+          <t>17,38; 23,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,68; 35,21</t>
+          <t>28,91; 35,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,89; 30,37</t>
+          <t>24,03; 30,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,52; 37,2</t>
+          <t>30,51; 37,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,49; 30,49</t>
+          <t>23,88; 29,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,85; 30,72</t>
+          <t>25,9; 30,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21,58; 26,12</t>
+          <t>21,54; 26,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,76; 33,65</t>
+          <t>29,01; 33,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,17; 24,9</t>
+          <t>21,6; 25,46</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,43</t>
+          <t>18,79; 21,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,39; 24,38</t>
+          <t>21,36; 24,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23,57; 26,71</t>
+          <t>23,88; 26,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,61</t>
+          <t>18,19; 21,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,29; 32,43</t>
+          <t>29,46; 32,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,06; 34,22</t>
+          <t>30,99; 34,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,33; 34,63</t>
+          <t>31,38; 34,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,74; 28,71</t>
+          <t>23,62; 26,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24,69; 26,78</t>
+          <t>24,59; 26,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26,86; 28,95</t>
+          <t>26,72; 28,89</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27,98; 30,13</t>
+          <t>28,02; 30,26</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,04; 24,15</t>
+          <t>21,32; 23,19</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>65193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>145453</t>
+          <t>146572</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37828; 63078</t>
+          <t>38633; 63797</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48491; 77202</t>
+          <t>46785; 76556</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54653; 84588</t>
+          <t>54571; 85427</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54749; 91250</t>
+          <t>52128; 81539</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53128; 80429</t>
+          <t>53174; 81096</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78682; 111428</t>
+          <t>80041; 113823</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76824; 109271</t>
+          <t>77825; 111636</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64302; 90125</t>
+          <t>68380; 95567</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97835; 135747</t>
+          <t>97868; 135569</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136640; 180498</t>
+          <t>137071; 183753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140103; 186633</t>
+          <t>139261; 183879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>125306; 170509</t>
+          <t>129175; 167109</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82237</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96653</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>178890</t>
+          <t>186213</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72656; 108973</t>
+          <t>72549; 107612</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87070; 126852</t>
+          <t>85097; 124800</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92625; 131183</t>
+          <t>91341; 129069</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65236; 103284</t>
+          <t>66106; 106784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>113522; 152600</t>
+          <t>113104; 151794</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>135454; 178809</t>
+          <t>135134; 177738</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>158613; 202954</t>
+          <t>159761; 204131</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82282; 114229</t>
+          <t>86078; 118193</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>199986; 252362</t>
+          <t>196190; 250557</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>233665; 292129</t>
+          <t>233604; 292834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260458; 321987</t>
+          <t>261845; 320513</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>152571; 204765</t>
+          <t>159063; 210241</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>139086</t>
+          <t>142311</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42150; 69221</t>
+          <t>41234; 68748</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71063; 104122</t>
+          <t>71657; 104259</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60297; 89417</t>
+          <t>60789; 89711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50275; 76724</t>
+          <t>52218; 78762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84818; 117647</t>
+          <t>86080; 118260</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>124334; 161628</t>
+          <t>125603; 163009</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88552; 122984</t>
+          <t>89288; 122811</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63191; 89203</t>
+          <t>66161; 91565</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>134957; 178139</t>
+          <t>133673; 176367</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>205438; 254617</t>
+          <t>205807; 254956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>156226; 201825</t>
+          <t>159171; 203943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>120197; 158467</t>
+          <t>123294; 160771</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70264</t>
+          <t>84027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>169846</t>
+          <t>113332</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>240110</t>
+          <t>197359</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42195; 67739</t>
+          <t>40299; 65824</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54738; 87879</t>
+          <t>56546; 88189</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73004; 106935</t>
+          <t>73407; 107662</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54691; 88119</t>
+          <t>66839; 106182</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101220; 138084</t>
+          <t>102568; 138303</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96441; 132919</t>
+          <t>96775; 132868</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>117570; 156097</t>
+          <t>117294; 154651</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>107930; 280018</t>
+          <t>96213; 132216</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>150511; 196106</t>
+          <t>151078; 193630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>159927; 207450</t>
+          <t>162940; 209062</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200765; 253883</t>
+          <t>198590; 248709</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>177203; 389559</t>
+          <t>172166; 222946</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>49037</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34332; 57447</t>
+          <t>34359; 57640</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40305; 65758</t>
+          <t>38805; 65707</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21380; 40431</t>
+          <t>20920; 42498</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12322; 25384</t>
+          <t>13472; 28537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61492; 90997</t>
+          <t>62363; 90884</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76896; 106509</t>
+          <t>76685; 104537</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40634; 64734</t>
+          <t>39889; 64372</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21589; 35346</t>
+          <t>23515; 37760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>102744; 139826</t>
+          <t>104116; 139964</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>122490; 164385</t>
+          <t>122861; 163847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65629; 98670</t>
+          <t>67886; 100625</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37341; 56650</t>
+          <t>39773; 61646</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>58387</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>110822</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>35173; 58654</t>
+          <t>35857; 60664</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>66652; 96044</t>
+          <t>67124; 97212</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90351; 124173</t>
+          <t>92806; 125237</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41237; 64685</t>
+          <t>41484; 63749</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71243; 102293</t>
+          <t>71090; 101798</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>94419; 125110</t>
+          <t>94173; 127151</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>114224; 147919</t>
+          <t>114079; 145237</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48860; 69128</t>
+          <t>49354; 70299</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>112870; 152568</t>
+          <t>112117; 152667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>167363; 211701</t>
+          <t>169460; 215172</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>213554; 261227</t>
+          <t>216274; 260503</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>96205; 128120</t>
+          <t>96196; 126628</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142546</t>
+          <t>162899</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>195802</t>
+          <t>241894</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>338348</t>
+          <t>404793</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>123633; 166821</t>
+          <t>124490; 166268</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>146797; 192626</t>
+          <t>144335; 189856</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128481; 173043</t>
+          <t>127398; 174156</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119500; 167981</t>
+          <t>140234; 190186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>191860; 238197</t>
+          <t>191445; 237466</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>199296; 247814</t>
+          <t>196901; 248367</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>163286; 211446</t>
+          <t>163228; 211150</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>96681; 266981</t>
+          <t>218652; 266565</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>327252; 389946</t>
+          <t>328178; 392468</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>358117; 423724</t>
+          <t>355312; 427053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>300721; 372252</t>
+          <t>302900; 370860</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>215058; 407238</t>
+          <t>368813; 439859</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>141677</t>
+          <t>158931</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>196561</t>
+          <t>221206</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>338238</t>
+          <t>380138</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>158329; 202540</t>
+          <t>156729; 205030</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134179; 180320</t>
+          <t>133715; 181031</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>198725; 248026</t>
+          <t>200198; 253690</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55091; 200790</t>
+          <t>138551; 183706</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>224690; 275843</t>
+          <t>226494; 280202</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>196335; 249600</t>
+          <t>197475; 253823</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>252178; 307372</t>
+          <t>252070; 310059</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>175717; 218814</t>
+          <t>198220; 242726</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>394828; 469207</t>
+          <t>395603; 470214</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>344612; 417047</t>
+          <t>344010; 415222</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>461517; 540034</t>
+          <t>465612; 538220</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>216706; 409777</t>
+          <t>351576; 414335</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>610391; 701611</t>
+          <t>615137; 706471</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>730173; 831885</t>
+          <t>728996; 833045</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>799914; 906779</t>
+          <t>810478; 907318</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>483831; 712631</t>
+          <t>642263; 746952</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>989297; 1095103</t>
+          <t>994968; 1102982</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1101719; 1213743</t>
+          <t>1099160; 1211669</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1110662; 1227594</t>
+          <t>1112386; 1217719</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>758693; 1050300</t>
+          <t>881086; 972095</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1642244; 1780854</t>
+          <t>1635480; 1776710</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1869143; 2015001</t>
+          <t>1859772; 2011120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1941723; 2090482</t>
+          <t>1944005; 2099412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1355095; 1718603</t>
+          <t>1547884; 1683892</t>
         </is>
       </c>
     </row>
